--- a/data/trans_dic/P16A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,72</t>
+          <t>5,15; 9,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 12,49</t>
+          <t>6,69; 12,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,81</t>
+          <t>3,91; 9,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 9,47</t>
+          <t>1,91; 10,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,83</t>
+          <t>4,46; 8,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 15,19</t>
+          <t>9,22; 15,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 15,01</t>
+          <t>8,36; 14,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,75</t>
+          <t>4,63; 13,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,35</t>
+          <t>5,42; 8,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,74</t>
+          <t>8,65; 12,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,77</t>
+          <t>6,75; 10,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,69</t>
+          <t>3,87; 9,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,43</t>
+          <t>3,16; 6,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 12,04</t>
+          <t>7,43; 12,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,47</t>
+          <t>6,63; 11,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,72</t>
+          <t>7,46; 15,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,19</t>
+          <t>5,46; 9,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 12,03</t>
+          <t>7,09; 11,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,6</t>
+          <t>6,38; 10,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,77</t>
+          <t>4,04; 9,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,55</t>
+          <t>4,85; 7,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,42</t>
+          <t>7,84; 11,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,38</t>
+          <t>7,04; 10,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 11,56</t>
+          <t>6,1; 11,37</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,43</t>
+          <t>4,3; 8,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,26</t>
+          <t>6,37; 10,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,54</t>
+          <t>5,56; 9,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 10,1</t>
+          <t>5,5; 10,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,89</t>
+          <t>5,41; 9,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,65</t>
+          <t>5,53; 9,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,27</t>
+          <t>6,05; 10,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,86</t>
+          <t>5,2; 8,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,34</t>
+          <t>5,51; 8,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,24</t>
+          <t>6,32; 9,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,27</t>
+          <t>6,48; 9,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,92</t>
+          <t>5,78; 8,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,59</t>
+          <t>3,53; 7,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,2</t>
+          <t>5,8; 10,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,56</t>
+          <t>4,43; 8,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,25</t>
+          <t>2,04; 7,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,33</t>
+          <t>2,62; 6,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,03</t>
+          <t>5,31; 10,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,22</t>
+          <t>5,06; 9,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,03</t>
+          <t>4,99; 8,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,58</t>
+          <t>3,42; 6,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,32</t>
+          <t>6,1; 9,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,21</t>
+          <t>5,25; 8,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,92</t>
+          <t>3,47; 6,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,65</t>
+          <t>4,62; 9,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,64</t>
+          <t>6,81; 12,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,78</t>
+          <t>5,53; 10,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,01</t>
+          <t>4,2; 7,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,75</t>
+          <t>3,26; 7,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,84</t>
+          <t>4,18; 8,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 11,1</t>
+          <t>5,97; 10,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,12</t>
+          <t>7,38; 11,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,84</t>
+          <t>4,51; 7,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,82</t>
+          <t>5,87; 9,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,0</t>
+          <t>6,43; 10,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,8</t>
+          <t>6,15; 8,8</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,04; 13,88</t>
+          <t>7,14; 13,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 14,31</t>
+          <t>7,42; 14,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 11,26</t>
+          <t>5,03; 10,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,69</t>
+          <t>6,02; 10,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,75</t>
+          <t>6,0; 12,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,25</t>
+          <t>4,85; 10,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,95</t>
+          <t>5,07; 10,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,55</t>
+          <t>2,08; 8,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,77</t>
+          <t>7,31; 11,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,26</t>
+          <t>6,51; 11,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,83</t>
+          <t>5,57; 9,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,6</t>
+          <t>2,98; 8,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 22,53</t>
+          <t>12,31; 22,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,01; 21,12</t>
+          <t>11,63; 21,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,56</t>
+          <t>8,76; 16,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,18</t>
+          <t>3,91; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,86</t>
+          <t>2,84; 7,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,02; 13,06</t>
+          <t>6,65; 12,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,85</t>
+          <t>5,96; 12,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,85</t>
+          <t>6,91; 10,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,07</t>
+          <t>7,03; 12,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,72</t>
+          <t>9,51; 14,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,88; 13,07</t>
+          <t>7,75; 12,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,18</t>
+          <t>6,43; 9,27</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,81</t>
+          <t>6,07; 7,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,67</t>
+          <t>8,38; 10,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,73</t>
+          <t>6,76; 8,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,67</t>
+          <t>5,08; 7,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,35</t>
+          <t>5,6; 7,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 9,31</t>
+          <t>7,42; 9,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,28</t>
+          <t>7,37; 9,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,12</t>
+          <t>5,86; 8,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,37</t>
+          <t>6,02; 7,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,58</t>
+          <t>8,14; 9,59</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,66</t>
+          <t>7,35; 8,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,73</t>
+          <t>5,96; 7,71</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25334; 48013</t>
+          <t>25426; 48044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30334; 56579</t>
+          <t>30324; 55834</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16941; 36967</t>
+          <t>16407; 38369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7803; 37880</t>
+          <t>7648; 42331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21052; 41271</t>
+          <t>20855; 41690</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38387; 65200</t>
+          <t>39576; 67039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34187; 59407</t>
+          <t>33088; 58278</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13566; 39923</t>
+          <t>14501; 41786</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52066; 80308</t>
+          <t>52131; 80994</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75001; 112447</t>
+          <t>76310; 112253</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56609; 87829</t>
+          <t>55056; 88107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28082; 69101</t>
+          <t>27622; 68154</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23768; 47262</t>
+          <t>23253; 46784</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50354; 82645</t>
+          <t>51014; 83566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38755; 67755</t>
+          <t>39174; 68408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32154; 66568</t>
+          <t>31597; 67512</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34908; 63753</t>
+          <t>34122; 61286</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42431; 73278</t>
+          <t>43178; 72806</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34836; 59757</t>
+          <t>35926; 60652</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20692; 49990</t>
+          <t>20641; 50885</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66327; 102751</t>
+          <t>66036; 102905</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>103063; 147908</t>
+          <t>101519; 146381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79572; 119772</t>
+          <t>81250; 118287</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59381; 108088</t>
+          <t>57033; 106308</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28106; 53756</t>
+          <t>27426; 51216</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43856; 76596</t>
+          <t>43334; 74500</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36984; 63854</t>
+          <t>37233; 64265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29030; 54189</t>
+          <t>29502; 55974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38293; 68218</t>
+          <t>37318; 67693</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39449; 68124</t>
+          <t>39058; 66915</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41276; 67921</t>
+          <t>39999; 68461</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28061; 48017</t>
+          <t>28167; 46740</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>72832; 110684</t>
+          <t>73084; 111439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88402; 128071</t>
+          <t>87609; 128895</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83329; 123393</t>
+          <t>86248; 121513</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63963; 96183</t>
+          <t>62344; 93471</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17302; 39393</t>
+          <t>18337; 38608</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33798; 62682</t>
+          <t>35654; 65093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28416; 55275</t>
+          <t>28617; 54342</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16043; 64363</t>
+          <t>18119; 67125</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13946; 32656</t>
+          <t>13528; 31613</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33834; 61602</t>
+          <t>32597; 61430</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33180; 59856</t>
+          <t>32818; 60434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35307; 57265</t>
+          <t>35542; 57093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36709; 68088</t>
+          <t>35377; 64732</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76151; 114567</t>
+          <t>74986; 119772</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68492; 106305</t>
+          <t>67947; 103568</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53377; 110690</t>
+          <t>55549; 111472</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18217; 37334</t>
+          <t>17862; 37791</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27617; 54125</t>
+          <t>29156; 55006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25914; 51533</t>
+          <t>26429; 50506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22731; 44850</t>
+          <t>23508; 44060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14012; 31316</t>
+          <t>13163; 30813</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18305; 39490</t>
+          <t>18680; 39925</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29647; 55155</t>
+          <t>29651; 54563</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39941; 60585</t>
+          <t>40212; 60195</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35500; 61980</t>
+          <t>35660; 61791</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52689; 85962</t>
+          <t>51392; 84171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60967; 97521</t>
+          <t>62659; 97987</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68771; 97235</t>
+          <t>67968; 97224</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20611; 40621</t>
+          <t>20903; 40518</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21832; 44057</t>
+          <t>22839; 45452</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17442; 37637</t>
+          <t>16812; 36062</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21786; 39360</t>
+          <t>22177; 39564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20227; 40308</t>
+          <t>20566; 41410</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16596; 36203</t>
+          <t>17122; 37616</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19521; 41363</t>
+          <t>19159; 39527</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14160; 52001</t>
+          <t>12643; 51197</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>45339; 74798</t>
+          <t>46474; 75478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43841; 74409</t>
+          <t>43008; 73112</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41421; 69978</t>
+          <t>39667; 67736</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33314; 83962</t>
+          <t>29091; 83057</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25730; 47279</t>
+          <t>25835; 46753</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27424; 52597</t>
+          <t>28970; 54206</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23548; 42559</t>
+          <t>22518; 42196</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11317; 23143</t>
+          <t>11056; 23186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9085; 26233</t>
+          <t>9468; 26433</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27158; 50499</t>
+          <t>25700; 49465</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24830; 51433</t>
+          <t>23859; 50699</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29881; 46051</t>
+          <t>29346; 45065</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38870; 65617</t>
+          <t>38224; 65845</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58506; 93569</t>
+          <t>60440; 94487</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51775; 85905</t>
+          <t>50905; 83714</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44377; 64922</t>
+          <t>45460; 65539</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>196981; 255794</t>
+          <t>198803; 256265</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>289602; 364737</t>
+          <t>286616; 357926</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>230616; 296394</t>
+          <t>229355; 294465</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>174870; 265333</t>
+          <t>175822; 267910</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>187296; 248215</t>
+          <t>189238; 247559</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>265277; 330185</t>
+          <t>262955; 336776</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>261087; 328950</t>
+          <t>261307; 330404</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>211773; 296798</t>
+          <t>214202; 295894</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>405507; 490355</t>
+          <t>400407; 487562</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>568021; 667252</t>
+          <t>566712; 667732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>508103; 600878</t>
+          <t>510177; 605538</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>428685; 549704</t>
+          <t>424323; 548369</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,72</t>
+          <t>5,13; 9,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 12,32</t>
+          <t>6,5; 12,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,15</t>
+          <t>3,94; 8,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,58</t>
+          <t>2,67; 10,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,92</t>
+          <t>4,3; 8,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 15,61</t>
+          <t>9,2; 15,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,73</t>
+          <t>8,68; 14,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 13,34</t>
+          <t>4,75; 13,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,42</t>
+          <t>5,42; 8,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 12,72</t>
+          <t>8,64; 12,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,81</t>
+          <t>6,81; 10,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,56</t>
+          <t>4,67; 10,04</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,36</t>
+          <t>3,21; 6,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,18</t>
+          <t>7,38; 12,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,58</t>
+          <t>6,32; 11,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,94</t>
+          <t>7,28; 15,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,8</t>
+          <t>5,66; 10,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,95</t>
+          <t>7,11; 11,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,76</t>
+          <t>6,48; 10,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,95</t>
+          <t>5,17; 10,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,56</t>
+          <t>4,93; 7,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,3</t>
+          <t>7,71; 11,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,25</t>
+          <t>7,05; 10,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 11,37</t>
+          <t>7,1; 11,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,03</t>
+          <t>4,31; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,96</t>
+          <t>6,23; 10,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,6</t>
+          <t>5,52; 9,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,44</t>
+          <t>5,27; 9,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,81</t>
+          <t>5,5; 9,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,35</t>
+          <t>6,06; 10,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,63</t>
+          <t>5,09; 8,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,4</t>
+          <t>5,6; 8,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,3</t>
+          <t>6,52; 9,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,13</t>
+          <t>6,34; 9,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,67</t>
+          <t>5,63; 8,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,44</t>
+          <t>3,51; 7,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,59</t>
+          <t>5,65; 10,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,41</t>
+          <t>4,5; 8,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,56</t>
+          <t>4,79; 8,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,13</t>
+          <t>2,86; 6,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 10,0</t>
+          <t>5,27; 9,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,31</t>
+          <t>5,29; 9,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,01</t>
+          <t>5,35; 8,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,26</t>
+          <t>3,49; 6,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,75</t>
+          <t>6,27; 9,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,0</t>
+          <t>5,23; 8,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,96</t>
+          <t>5,43; 7,88</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,77</t>
+          <t>4,56; 9,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,84</t>
+          <t>6,76; 13,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,57</t>
+          <t>5,27; 10,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,86</t>
+          <t>4,03; 7,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,63</t>
+          <t>3,36; 7,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,94</t>
+          <t>4,19; 8,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,98</t>
+          <t>5,71; 11,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,05</t>
+          <t>7,38; 10,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,81</t>
+          <t>4,62; 7,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,62</t>
+          <t>5,83; 9,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,05</t>
+          <t>6,21; 9,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,8</t>
+          <t>6,2; 8,74</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,85</t>
+          <t>6,91; 13,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,42; 14,77</t>
+          <t>7,19; 14,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,79</t>
+          <t>5,24; 10,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,75</t>
+          <t>5,92; 10,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,08</t>
+          <t>5,89; 11,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,65</t>
+          <t>4,68; 10,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,46</t>
+          <t>5,0; 10,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,42</t>
+          <t>6,27; 10,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,88</t>
+          <t>7,27; 11,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,06</t>
+          <t>6,63; 11,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,51</t>
+          <t>5,73; 9,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,51</t>
+          <t>6,67; 9,6</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,31; 22,28</t>
+          <t>12,09; 22,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 21,77</t>
+          <t>11,76; 21,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 16,42</t>
+          <t>9,05; 16,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,2</t>
+          <t>3,92; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,92</t>
+          <t>2,71; 7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 12,79</t>
+          <t>6,75; 12,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,67</t>
+          <t>6,06; 13,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,62</t>
+          <t>7,03; 10,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,11</t>
+          <t>7,1; 12,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,86</t>
+          <t>9,35; 14,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,74</t>
+          <t>7,87; 13,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,27</t>
+          <t>6,13; 9,13</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,82</t>
+          <t>6,11; 7,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,47</t>
+          <t>8,38; 10,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,68</t>
+          <t>6,81; 8,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,75</t>
+          <t>6,27; 8,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 7,33</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,5</t>
+          <t>7,3; 9,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,32</t>
+          <t>7,4; 9,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,09</t>
+          <t>6,98; 8,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,33</t>
+          <t>6,1; 7,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 9,59</t>
+          <t>8,17; 9,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,73</t>
+          <t>7,4; 8,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,71</t>
+          <t>6,89; 8,12</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>53740</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25426; 48044</t>
+          <t>25347; 48423</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30324; 55834</t>
+          <t>29464; 54465</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16407; 38369</t>
+          <t>16547; 37317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7648; 42331</t>
+          <t>10883; 42504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20855; 41690</t>
+          <t>20122; 41382</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39576; 67039</t>
+          <t>39482; 67259</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33088; 58278</t>
+          <t>34371; 59183</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14501; 41786</t>
+          <t>17231; 47205</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52131; 80994</t>
+          <t>52096; 82202</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76310; 112253</t>
+          <t>76235; 110630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55056; 88107</t>
+          <t>55501; 87917</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27622; 68154</t>
+          <t>35960; 77325</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83321</t>
+          <t>89235</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23253; 46784</t>
+          <t>23574; 47420</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51014; 83566</t>
+          <t>50610; 83930</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39174; 68408</t>
+          <t>37325; 65714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31597; 67512</t>
+          <t>34698; 73216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34122; 61286</t>
+          <t>35376; 64882</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43178; 72806</t>
+          <t>43314; 71347</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35926; 60652</t>
+          <t>36546; 61168</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20641; 50885</t>
+          <t>25912; 51630</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66036; 102905</t>
+          <t>67097; 101015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101519; 146381</t>
+          <t>99823; 144159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81250; 118287</t>
+          <t>81342; 121362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57033; 106308</t>
+          <t>69405; 114588</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40345</t>
+          <t>45797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76830</t>
+          <t>87121</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27426; 51216</t>
+          <t>27487; 52731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43334; 74500</t>
+          <t>42335; 73311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37233; 64265</t>
+          <t>36938; 63527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29502; 55974</t>
+          <t>32707; 60826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37318; 67693</t>
+          <t>37929; 68278</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39058; 66915</t>
+          <t>39043; 66904</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39999; 68461</t>
+          <t>40072; 67500</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28167; 46740</t>
+          <t>31606; 52898</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73084; 111439</t>
+          <t>74340; 110860</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87609; 128895</t>
+          <t>90423; 129998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86248; 121513</t>
+          <t>84374; 122647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62344; 93471</t>
+          <t>69949; 104633</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>46093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45697</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87885</t>
+          <t>95414</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18337; 38608</t>
+          <t>18226; 38490</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35654; 65093</t>
+          <t>34745; 64511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28617; 54342</t>
+          <t>29091; 55662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18119; 67125</t>
+          <t>33584; 62910</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13528; 31613</t>
+          <t>14750; 33982</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32597; 61430</t>
+          <t>32360; 60370</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32818; 60434</t>
+          <t>34311; 61548</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35542; 57093</t>
+          <t>39405; 60376</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35377; 64732</t>
+          <t>36148; 66378</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74986; 119772</t>
+          <t>77099; 115668</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67947; 103568</t>
+          <t>67715; 104068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55549; 111472</t>
+          <t>78079; 113215</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>55336</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82289</t>
+          <t>90226</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17862; 37791</t>
+          <t>17647; 37417</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29156; 55006</t>
+          <t>28954; 56656</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26429; 50506</t>
+          <t>25194; 50012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23508; 44060</t>
+          <t>24493; 46831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13163; 30813</t>
+          <t>13578; 31507</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18680; 39925</t>
+          <t>18724; 40033</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29651; 54563</t>
+          <t>28351; 55216</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40212; 60195</t>
+          <t>44808; 66637</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35660; 61791</t>
+          <t>36536; 62000</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51392; 84171</t>
+          <t>50984; 84393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62659; 97987</t>
+          <t>60493; 96252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>67968; 97224</t>
+          <t>75403; 106216</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29875</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61780</t>
+          <t>68046</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20903; 40518</t>
+          <t>20224; 40880</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22839; 45452</t>
+          <t>22133; 44807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16812; 36062</t>
+          <t>17529; 35648</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22177; 39564</t>
+          <t>24080; 42423</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20566; 41410</t>
+          <t>20211; 40352</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17122; 37616</t>
+          <t>16509; 36551</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19159; 39527</t>
+          <t>18881; 41014</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12643; 51197</t>
+          <t>27548; 44618</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46474; 75478</t>
+          <t>46185; 75457</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43008; 73112</t>
+          <t>43804; 74757</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39667; 67736</t>
+          <t>40787; 69044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29091; 83057</t>
+          <t>56432; 81230</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>37388</t>
+          <t>40629</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53736</t>
+          <t>58210</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25835; 46753</t>
+          <t>25372; 46448</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28970; 54206</t>
+          <t>29276; 53795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22518; 42196</t>
+          <t>23248; 43368</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11056; 23186</t>
+          <t>12164; 25450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9468; 26433</t>
+          <t>9039; 24798</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25700; 49465</t>
+          <t>26104; 49228</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23859; 50699</t>
+          <t>24232; 52415</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29346; 45065</t>
+          <t>32552; 50716</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38224; 65845</t>
+          <t>38611; 66554</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60440; 94487</t>
+          <t>59476; 94407</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50905; 83714</t>
+          <t>51745; 86659</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45460; 65539</t>
+          <t>47384; 70581</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>490123</t>
+          <t>541992</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>198803; 256265</t>
+          <t>200192; 258625</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>286616; 357926</t>
+          <t>286621; 359400</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>229355; 294465</t>
+          <t>231227; 294228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>175822; 267910</t>
+          <t>221574; 293991</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>189238; 247559</t>
+          <t>190866; 247570</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>262955; 336776</t>
+          <t>258865; 330169</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>261307; 330404</t>
+          <t>262304; 330691</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>214202; 295894</t>
+          <t>260374; 318892</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>400407; 487562</t>
+          <t>405828; 486224</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>566712; 667732</t>
+          <t>569144; 671198</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>510177; 605538</t>
+          <t>513221; 608988</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>424323; 548369</t>
+          <t>500101; 589879</t>
         </is>
       </c>
     </row>
